--- a/target/ExcelForm.xlsx
+++ b/target/ExcelForm.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>Krishnaraj</t>
   </si>
@@ -70,12 +70,34 @@
   </si>
   <si>
     <t>Santhosh</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Form submitted successfully</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Full Name is required</t>
+  </si>
+  <si>
+    <t>Please select an experience level</t>
+  </si>
+  <si>
+    <t>Remote Preference is required</t>
+  </si>
+  <si>
+    <t>I agree to terms is required</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -447,12 +469,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.6640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.5546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.21875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="27.88671875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -488,8 +510,12 @@
       <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
@@ -504,8 +530,12 @@
       <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2"/>
@@ -518,8 +548,12 @@
       <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
@@ -532,8 +566,12 @@
       <c r="D5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
@@ -546,8 +584,12 @@
       <c r="D6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="7" t="s">
@@ -562,8 +604,12 @@
       <c r="D7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
